--- a/result_plot.xlsx
+++ b/result_plot.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,10 +446,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.357711859946298</v>
+        <v>0.7308111426897878</v>
       </c>
       <c r="C2" t="n">
-        <v>1.445060543318361</v>
+        <v>0.9968489953357147</v>
       </c>
     </row>
     <row r="3">
@@ -457,10 +457,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.177101092676132</v>
+        <v>1.869383003025954</v>
       </c>
       <c r="C3" t="n">
-        <v>1.021372327867545</v>
+        <v>1.784575176870166</v>
       </c>
     </row>
     <row r="4">
@@ -468,10 +468,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.257183285794906</v>
+        <v>0.7460610526599197</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8292637134318226</v>
+        <v>0.8184139314910657</v>
       </c>
     </row>
     <row r="5">
@@ -479,10 +479,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1079627603692477</v>
+        <v>0.6883454773711541</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0575689215555842</v>
+        <v>0.8381688988424383</v>
       </c>
     </row>
     <row r="6">
@@ -490,10 +490,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.2727757345541271</v>
+        <v>1.331349584579566</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.271106501000612</v>
+        <v>0.7802540247438383</v>
       </c>
     </row>
     <row r="7">
@@ -501,10 +501,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>1.102969875385327</v>
+        <v>0.6573400897403524</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8665054922089546</v>
+        <v>0.7861268446943415</v>
       </c>
     </row>
     <row r="8">
@@ -512,10 +512,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.530586042353288</v>
+        <v>0.7007608336988702</v>
       </c>
       <c r="C8" t="n">
-        <v>1.431342668041456</v>
+        <v>0.6785835848844064</v>
       </c>
     </row>
     <row r="9">
@@ -523,10 +523,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.512422572187459</v>
+        <v>0.6424263798412341</v>
       </c>
       <c r="C9" t="n">
-        <v>1.326522362367516</v>
+        <v>0.8659268785759737</v>
       </c>
     </row>
     <row r="10">
@@ -534,10 +534,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.06454055545951194</v>
+        <v>0.6696265582909722</v>
       </c>
       <c r="C10" t="n">
-        <v>0.09808213249668903</v>
+        <v>0.9092684834933733</v>
       </c>
     </row>
     <row r="11">
@@ -545,10 +545,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.326908086284963</v>
+        <v>1.040984099088739</v>
       </c>
       <c r="C11" t="n">
-        <v>0.4930439269069595</v>
+        <v>0.8617859294743869</v>
       </c>
     </row>
     <row r="12">
@@ -556,10 +556,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.9278158813199752</v>
+        <v>0.7319191038531908</v>
       </c>
       <c r="C12" t="n">
-        <v>0.6327201101314722</v>
+        <v>0.7687381415381758</v>
       </c>
     </row>
     <row r="13">
@@ -567,10 +567,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.1040639622542105</v>
+        <v>1.892688162615314</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.0750666826457045</v>
+        <v>0.9036525211998199</v>
       </c>
     </row>
     <row r="14">
@@ -578,10 +578,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.128340864541109</v>
+        <v>0.9113367233053141</v>
       </c>
       <c r="C14" t="n">
-        <v>0.273906260536973</v>
+        <v>1.149948019183705</v>
       </c>
     </row>
     <row r="15">
@@ -589,10 +589,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.423449392167355</v>
+        <v>0.8602475550630733</v>
       </c>
       <c r="C15" t="n">
-        <v>1.352917656852177</v>
+        <v>0.6700918958532395</v>
       </c>
     </row>
     <row r="16">
@@ -600,10 +600,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.068763228083889</v>
+        <v>1.110654022194552</v>
       </c>
       <c r="C16" t="n">
-        <v>1.188022234558819</v>
+        <v>1.311059492936431</v>
       </c>
     </row>
     <row r="17">
@@ -611,10 +611,10 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>-0</v>
+        <v>0.6496780968645733</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9699443942875953</v>
+        <v>0.8313030386725309</v>
       </c>
     </row>
     <row r="18">
@@ -622,10 +622,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.716655020340109</v>
+        <v>0.6543809456796766</v>
       </c>
       <c r="C18" t="n">
-        <v>1.404507746021981</v>
+        <v>0.6925044007212602</v>
       </c>
     </row>
     <row r="19">
@@ -633,10 +633,10 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.4918655781200493</v>
+        <v>0.6604760221770372</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8875171187960678</v>
+        <v>0.9517649854309171</v>
       </c>
     </row>
     <row r="20">
@@ -644,10 +644,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.359707083568872</v>
+        <v>1.069500705902748</v>
       </c>
       <c r="C20" t="n">
-        <v>1.404673543805121</v>
+        <v>1.150332910391084</v>
       </c>
     </row>
     <row r="21">
@@ -655,10 +655,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.058497435216706</v>
+        <v>0.6518485476764746</v>
       </c>
       <c r="C21" t="n">
-        <v>1.25223726950129</v>
+        <v>0.7328427570509526</v>
       </c>
     </row>
     <row r="22">
@@ -666,10 +666,10 @@
         <v>20</v>
       </c>
       <c r="B22" t="n">
-        <v>1.814128589207219</v>
+        <v>0.8968418963290693</v>
       </c>
       <c r="C22" t="n">
-        <v>1.100755594753193</v>
+        <v>0.9672836922927908</v>
       </c>
     </row>
     <row r="23">
@@ -677,10 +677,10 @@
         <v>21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.9078746688001189</v>
+        <v>0.6549228808038251</v>
       </c>
       <c r="C23" t="n">
-        <v>1.070260436591865</v>
+        <v>0.8668717089954834</v>
       </c>
     </row>
     <row r="24">
@@ -688,10 +688,10 @@
         <v>22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.5876978117800268</v>
+        <v>1.618592406068</v>
       </c>
       <c r="C24" t="n">
-        <v>0.4055850634378479</v>
+        <v>1.662337768515959</v>
       </c>
     </row>
     <row r="25">
@@ -699,10 +699,10 @@
         <v>23</v>
       </c>
       <c r="B25" t="n">
-        <v>-0.01440320079401098</v>
+        <v>0.9392608050043025</v>
       </c>
       <c r="C25" t="n">
-        <v>0.166059623966322</v>
+        <v>0.9306992471172846</v>
       </c>
     </row>
     <row r="26">
@@ -710,10 +710,10 @@
         <v>24</v>
       </c>
       <c r="B26" t="n">
-        <v>1.346654086043043</v>
+        <v>0.6589831669507411</v>
       </c>
       <c r="C26" t="n">
-        <v>1.420824367254024</v>
+        <v>0.7584051831686356</v>
       </c>
     </row>
     <row r="27">
@@ -721,10 +721,10 @@
         <v>25</v>
       </c>
       <c r="B27" t="n">
-        <v>1.208985192288026</v>
+        <v>1.81786444595756</v>
       </c>
       <c r="C27" t="n">
-        <v>1.440329616449348</v>
+        <v>1.589054782841111</v>
       </c>
     </row>
     <row r="28">
@@ -732,10 +732,10 @@
         <v>26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.292415729036002</v>
+        <v>2.314329015142553</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2057776728067595</v>
+        <v>2.08230301623734</v>
       </c>
     </row>
     <row r="29">
@@ -743,10 +743,10 @@
         <v>27</v>
       </c>
       <c r="B29" t="n">
-        <v>1.387851091238581</v>
+        <v>0.6954539536452551</v>
       </c>
       <c r="C29" t="n">
-        <v>1.364603045374128</v>
+        <v>0.8186115464355961</v>
       </c>
     </row>
     <row r="30">
@@ -754,10 +754,10 @@
         <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.807365612511445</v>
+        <v>0.8174339011359423</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8923226117870633</v>
+        <v>0.701633048765252</v>
       </c>
     </row>
     <row r="31">
@@ -765,10 +765,10 @@
         <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>1.5545193397367</v>
+        <v>2.415913174407361</v>
       </c>
       <c r="C31" t="n">
-        <v>1.242952836857692</v>
+        <v>2.245664732535145</v>
       </c>
     </row>
     <row r="32">
@@ -776,10 +776,10 @@
         <v>30</v>
       </c>
       <c r="B32" t="n">
-        <v>0.9129682668270873</v>
+        <v>0.7618587789501594</v>
       </c>
       <c r="C32" t="n">
-        <v>1.141782072985103</v>
+        <v>0.8331903654762143</v>
       </c>
     </row>
     <row r="33">
@@ -787,10 +787,10 @@
         <v>31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.8352410350352667</v>
+        <v>0.700503694097571</v>
       </c>
       <c r="C33" t="n">
-        <v>0.6419585341020521</v>
+        <v>0.7756010848915257</v>
       </c>
     </row>
     <row r="34">
@@ -798,10 +798,32 @@
         <v>32</v>
       </c>
       <c r="B34" t="n">
-        <v>1.298584773192212</v>
+        <v>2.135403233921381</v>
       </c>
       <c r="C34" t="n">
-        <v>1.318223249769135</v>
+        <v>1.951033191693567</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>0.716336479916482</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.9883054764585877</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1.121906832783492</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.7808401431531058</v>
       </c>
     </row>
   </sheetData>
@@ -815,7 +837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -835,10 +857,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.463906444830943</v>
+        <v>0.9449807858251712</v>
       </c>
       <c r="C2" t="n">
-        <v>1.159163175901932</v>
+        <v>0.8924060308934316</v>
       </c>
     </row>
     <row r="3">
@@ -846,10 +868,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.554565631204025</v>
+        <v>1.468191356379455</v>
       </c>
       <c r="C3" t="n">
-        <v>1.34975895301379</v>
+        <v>1.631578791451491</v>
       </c>
     </row>
     <row r="4">
@@ -857,10 +879,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>0.9884179104413243</v>
+        <v>1.461638357134317</v>
       </c>
       <c r="C4" t="n">
-        <v>1.065995915639506</v>
+        <v>1.678718055917217</v>
       </c>
     </row>
     <row r="5">
@@ -868,10 +890,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>0.8975888105975592</v>
+        <v>0.7526272740955297</v>
       </c>
       <c r="C5" t="n">
-        <v>1.016006666504662</v>
+        <v>0.9975442449420626</v>
       </c>
     </row>
     <row r="6">
@@ -879,10 +901,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.286771364943156</v>
+        <v>0.6855022180771014</v>
       </c>
       <c r="C6" t="n">
-        <v>1.049033163240474</v>
+        <v>0.7956003572142919</v>
       </c>
     </row>
     <row r="7">
@@ -890,10 +912,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>0.3667086227617696</v>
+        <v>0.7210475875492813</v>
       </c>
       <c r="C7" t="n">
-        <v>0.7017998700921007</v>
+        <v>0.9066231647981535</v>
       </c>
     </row>
     <row r="8">
@@ -901,10 +923,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418643027864877</v>
+        <v>0.9120792238832838</v>
       </c>
       <c r="C8" t="n">
-        <v>1.381873103974812</v>
+        <v>1.628485606219772</v>
       </c>
     </row>
     <row r="9">
@@ -912,10 +934,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.549347648714219</v>
+        <v>0.8030548105529498</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8546841135800844</v>
+        <v>0.851297433294921</v>
       </c>
     </row>
     <row r="10">
@@ -923,10 +945,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9434188829562924</v>
+        <v>0.781070093469339</v>
       </c>
       <c r="C10" t="n">
-        <v>1.126597914233349</v>
+        <v>1.090448892628197</v>
       </c>
     </row>
     <row r="11">
@@ -934,10 +956,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.510024491860028</v>
+        <v>1.74142058273354</v>
       </c>
       <c r="C11" t="n">
-        <v>1.449790813100737</v>
+        <v>1.64171566394049</v>
       </c>
     </row>
     <row r="12">
@@ -945,10 +967,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.249103445463394</v>
+        <v>0.7128778730616214</v>
       </c>
       <c r="C12" t="n">
-        <v>1.2765612497701</v>
+        <v>0.7641297430561487</v>
       </c>
     </row>
     <row r="13">
@@ -956,10 +978,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.601190117650639</v>
+        <v>0.6429462194408853</v>
       </c>
       <c r="C13" t="n">
-        <v>1.407553459589127</v>
+        <v>0.7992191668263926</v>
       </c>
     </row>
     <row r="14">
@@ -967,10 +989,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.502114486865029</v>
+        <v>0.7400546845693606</v>
       </c>
       <c r="C14" t="n">
-        <v>0.9419387606590108</v>
+        <v>0.955681525803918</v>
       </c>
     </row>
     <row r="15">
@@ -978,10 +1000,10 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.266800786562561</v>
+        <v>0.7386861457942482</v>
       </c>
       <c r="C15" t="n">
-        <v>1.258554298430562</v>
+        <v>0.9634495105341072</v>
       </c>
     </row>
     <row r="16">
@@ -989,10 +1011,21 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.354955526294634</v>
+        <v>0.6751742776695879</v>
       </c>
       <c r="C16" t="n">
-        <v>1.41019998607367</v>
+        <v>0.8419555161349903</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>0.6832257383321263</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.063466963637261</v>
       </c>
     </row>
   </sheetData>
